--- a/docs/public/downloads/property-checklist.xlsx
+++ b/docs/public/downloads/property-checklist.xlsx
@@ -133,7 +133,7 @@
     <t>上位店への提出前に内容を再確認した</t>
   </si>
   <si>
-    <t>契約前に上位店の確認を受けることを理解した</t>
+    <t>契約前に上位店のアドバイスを受け、開設者が最終決定することを理解した</t>
   </si>
 </sst>
 </file>
